--- a/server/public/docs/template-form.xlsx
+++ b/server/public/docs/template-form.xlsx
@@ -661,6 +661,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="3" t="inlineStr">
@@ -689,10 +690,11 @@
       <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>· ③ 인터넷+TV 사은품: 종류 / SK-매장 / SK-온라인 / KT-매장 / KT-온라인 / LG-매장 / LG-온라인 / 비고</t>
-        </is>
-      </c>
-    </row>
+          <t>· ③ 인터넷+TV 사은품: 종류 / SK / KT / LG / 비고 (통합 1개 · 온·오프라인 공통)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="3" t="inlineStr">
@@ -721,10 +723,11 @@
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>· 인터넷+TV 사은품 1행 (3사 × 2채널 = 6칸)</t>
-        </is>
-      </c>
-    </row>
+          <t>· 인터넷+TV 사은품 1행 (3사 컬럼 · 통합 1개)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="3" t="inlineStr">
@@ -757,6 +760,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="3" t="inlineStr">
@@ -797,6 +801,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="3" t="inlineStr">
@@ -2435,23 +2440,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>📡 인터넷+TV 사은품 · 통신사 × 채널별 금액</t>
+          <t>📡 인터넷+TV 사은품 · 3사 통합 1개 (온·오프라인 공통)</t>
         </is>
       </c>
     </row>
@@ -2463,35 +2465,20 @@
       </c>
       <c r="B2" s="17" t="inlineStr">
         <is>
-          <t>SK-매장</t>
-        </is>
-      </c>
-      <c r="C2" s="18" t="inlineStr">
-        <is>
-          <t>SK-온라인</t>
-        </is>
-      </c>
-      <c r="D2" s="13" t="inlineStr">
-        <is>
-          <t>KT-매장</t>
-        </is>
-      </c>
-      <c r="E2" s="19" t="inlineStr">
-        <is>
-          <t>KT-온라인</t>
-        </is>
-      </c>
-      <c r="F2" s="20" t="inlineStr">
-        <is>
-          <t>LG-매장</t>
-        </is>
-      </c>
-      <c r="G2" s="21" t="inlineStr">
-        <is>
-          <t>LG-온라인</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -2506,22 +2493,13 @@
       <c r="B3" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="C3" s="22" t="n">
-        <v>40</v>
-      </c>
-      <c r="D3" s="23" t="n">
+      <c r="C3" s="23" t="n">
         <v>60</v>
       </c>
-      <c r="E3" s="23" t="n">
-        <v>50</v>
-      </c>
-      <c r="F3" s="24" t="n">
+      <c r="D3" s="24" t="n">
         <v>55</v>
       </c>
-      <c r="G3" s="24" t="n">
-        <v>45</v>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>만원 · 샘플</t>
         </is>
@@ -2530,14 +2508,14 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>※ 현금 페이백 · 통신사 × 채널(매장/온라인)별 금액 · 단위: 만원 · 샘플 값 입력됨</t>
+          <t>※ 인터넷+TV 정책은 온·오프라인 통합 1개 (매트릭스 참조) · 사은품은 3사별 현금 페이백 금액만 등록 · 단위: 만원</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A4:E4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/server/public/docs/template-form.xlsx
+++ b/server/public/docs/template-form.xlsx
@@ -84,7 +84,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -129,56 +129,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00dc2626"/>
+        <bgColor rgb="00dc2626"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="002563eb"/>
         <bgColor rgb="002563eb"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00059669"/>
-        <bgColor rgb="00059669"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00eff6ff"/>
-        <bgColor rgb="00eff6ff"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00f0fdf4"/>
-        <bgColor rgb="00f0fdf4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00dc2626"/>
-        <bgColor rgb="00dc2626"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00991b1b"/>
-        <bgColor rgb="00991b1b"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001e40af"/>
-        <bgColor rgb="001e40af"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00e40981"/>
         <bgColor rgb="00e40981"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009d174d"/>
-        <bgColor rgb="009d174d"/>
       </patternFill>
     </fill>
   </fills>
@@ -208,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -252,25 +216,7 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -647,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -657,16 +603,15 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>봉이모바일 공통폼 템플릿 (오프라인+온라인 통합)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+          <t>봉이모바일 공통폼 템플릿 (매장/온라인 공용)</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>📌 컬럼 구조</t>
+          <t>📌 공통폼</t>
         </is>
       </c>
     </row>
@@ -674,7 +619,7 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>· ① 무선: 통신사 / 펫네임 / 요금제(월요금) / 번이 / 기변 (오프라인·온라인 공통 · 값 동일)</t>
+          <t>· 한 개 템플릿 파일을 오프라인(12개 매장)과 온라인(1개 통합)이 각자 복사해서 사용</t>
         </is>
       </c>
     </row>
@@ -682,7 +627,7 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>· ② 유심: 통신사 / 요금제(월요금) / 25%↓실납 / 번이-매장 / 번이-온라인</t>
+          <t>· 구조 동일 · 매장/온라인이 자기 채널 값만 입력</t>
         </is>
       </c>
     </row>
@@ -690,16 +635,15 @@
       <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>· ③ 인터넷+TV 사은품: 종류 / SK / KT / LG / 비고 (통합 1개 · 온·오프라인 공통)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+          <t>· 저장 시 파일명 구분 (예: template-form-상무점.xlsx / template-form-온라인.xlsx)</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>📊 데이터</t>
+          <t>📊 시트 구조</t>
         </is>
       </c>
     </row>
@@ -707,7 +651,7 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>· 무선 54행 (정리3 원본)</t>
+          <t>· ① 무선(휴대폰): 통신사/펫네임/요금제(월요금)/번이/기변 · 54행</t>
         </is>
       </c>
     </row>
@@ -715,7 +659,7 @@
       <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>· 유심 9행 (매장·온라인 페이백 한 행에 병렬 표기)</t>
+          <t>· ② 유심: 통신사/요금제(월요금)/25%↓실납/번이 · 9행</t>
         </is>
       </c>
     </row>
@@ -723,11 +667,10 @@
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>· 인터넷+TV 사은품 1행 (3사 컬럼 · 통합 1개)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>· ③ 인터넷+TV 사은품: 종류/SK/KT/LG/비고 · 1행 (통합 1개 · 온·오프라인 공통)</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="3" t="inlineStr">
@@ -760,7 +703,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="3" t="inlineStr">
@@ -781,7 +723,7 @@
       <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>· 선택약정 25% 할인 (SK/KT 개통시 · LG 개통 후 고객센터 신청) · 실납 = 월요금 × 0.75</t>
+          <t>· 선택약정 25% 할인 (SK/KT 개통시 · LG 개통 후 고객센터 신청)</t>
         </is>
       </c>
     </row>
@@ -801,7 +743,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="3" t="inlineStr">
@@ -822,7 +763,7 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>· 매장 컬럼(파란 배경) = 오프라인 12개 매장 공통 적용</t>
+          <t>· PK: 무선=(통신사+펫네임+요금제) · 유심=(통신사+요금제) · 사은품=(종류)</t>
         </is>
       </c>
     </row>
@@ -830,15 +771,7 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>· 온라인 컬럼(초록 배경) = 온라인 통합 1개 적용</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>· PK: 무선=(통신사+펫네임+요금제) · 유심=(통신사+요금제) · 새 기종/요금제는 행 추가</t>
+          <t>· 샘플 값 입력됨 → 실제 정책으로 덮어쓰기</t>
         </is>
       </c>
     </row>
@@ -856,7 +789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -869,7 +802,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>📱 무선(휴대폰) 시세 · 54행 (오프라인·온라인 공통)</t>
+          <t>📱 무선(휴대폰) 시세 · 54행</t>
         </is>
       </c>
     </row>
@@ -2142,17 +2075,19 @@
         <v>114</v>
       </c>
     </row>
-    <row r="57" ht="45" customHeight="1">
-      <c r="A57" s="12" t="inlineStr">
-        <is>
-          <t>※ 번이/기변(만원) = 공시지원금 기준 현금완납가 · 음수=페이백(초록) · 양수=부담(빨강) · 오프라인/온라인 값 동일</t>
+    <row r="58" ht="80" customHeight="1">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>※ 번이/기변(만원) = 공시지원금 기준 현금완납가 · 음수=페이백(초록) · 양수=부담(빨강)
+※ 요금제: SK 프리미엄 · KT 초이스스페셜 · LG 프리미어 슈퍼
+※ 새 기종은 행 추가 · 컬럼 고정</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A58:E58"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A57:E57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2164,20 +2099,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>📇 유심 시세 · 9행 · 매장/온라인 병렬</t>
+          <t>📇 유심 시세 · 9행 (샘플 값 포함)</t>
         </is>
       </c>
     </row>
@@ -2197,14 +2131,9 @@
           <t>25%↓실납</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
-        <is>
-          <t>번이-매장</t>
-        </is>
-      </c>
-      <c r="E2" s="14" t="inlineStr">
-        <is>
-          <t>번이-온라인</t>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>번이</t>
         </is>
       </c>
     </row>
@@ -2224,11 +2153,8 @@
           <t>24,750</t>
         </is>
       </c>
-      <c r="D3" s="15" t="n">
+      <c r="D3" s="8" t="n">
         <v>-40</v>
-      </c>
-      <c r="E3" s="16" t="n">
-        <v>-25</v>
       </c>
     </row>
     <row r="4">
@@ -2247,11 +2173,8 @@
           <t>33,750</t>
         </is>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="8" t="n">
         <v>-35</v>
-      </c>
-      <c r="E4" s="16" t="n">
-        <v>-30</v>
       </c>
     </row>
     <row r="5">
@@ -2270,11 +2193,8 @@
           <t>41,250</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="8" t="n">
         <v>-40</v>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>-35</v>
       </c>
     </row>
     <row r="6">
@@ -2293,11 +2213,8 @@
           <t>27,750</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="8" t="n">
         <v>-15</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>-5</v>
       </c>
     </row>
     <row r="7">
@@ -2316,11 +2233,8 @@
           <t>37,500</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="8" t="n">
         <v>-20</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>-10</v>
       </c>
     </row>
     <row r="8">
@@ -2339,11 +2253,8 @@
           <t>51,750</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="8" t="n">
         <v>-25</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-15</v>
       </c>
     </row>
     <row r="9">
@@ -2362,10 +2273,7 @@
           <t>24,750</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
-        <v>-15</v>
-      </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="8" t="n">
         <v>-15</v>
       </c>
     </row>
@@ -2385,11 +2293,8 @@
           <t>45,750</t>
         </is>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="8" t="n">
         <v>-30</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>-25</v>
       </c>
     </row>
     <row r="11">
@@ -2408,27 +2313,24 @@
           <t>63,750</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="8" t="n">
         <v>-40</v>
       </c>
-      <c r="E11" s="16" t="n">
-        <v>-35</v>
-      </c>
-    </row>
-    <row r="12" ht="80" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>※ 유심은 MNP 전용 · 펫네임/기변 없음 · 번이 만원 · 음수=페이백
-※ 번이-매장 (파란 배경) = 오프라인 12개 매장 공통 적용 · 번이-온라인 (초록 배경) = 온라인 통합
-※ 실납 = 월요금 × 0.75 (선택약정 25% · SK/KT 개통시 · LG 개통 후 고객센터)
+    </row>
+    <row r="13" ht="80" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>※ 유심은 MNP(번호이동) 전용 · 펫네임/기변 없음 · 번이(만원)만 입력
+※ 실납 = 월요금 × 0.75 (선택약정 25% 할인 · SK/KT 개통시 · LG 개통 후 고객센터 신청)
+※ 샘플 값 입력됨 — 매장/온라인이 각자 자기 페이백 값으로 덮어쓰기
 ※ 유심비: SK/LG 다음 달 청구 · KT 선납 · 유지기간: SK M+6 / KT·LG 183일</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2453,7 +2355,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>📡 인터넷+TV 사은품 · 3사 통합 1개 (온·오프라인 공통)</t>
+          <t>📡 인터넷+TV 사은품 · 통합 1개 (온·오프라인 공통)</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2365,17 @@
           <t>종류</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="D2" s="20" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
@@ -2490,13 +2392,13 @@
           <t>현금</t>
         </is>
       </c>
-      <c r="B3" s="22" t="n">
+      <c r="B3" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="C3" s="23" t="n">
+      <c r="C3" s="17" t="n">
         <v>60</v>
       </c>
-      <c r="D3" s="24" t="n">
+      <c r="D3" s="18" t="n">
         <v>55</v>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -2508,7 +2410,7 @@
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>※ 인터넷+TV 정책은 온·오프라인 통합 1개 (매트릭스 참조) · 사은품은 3사별 현금 페이백 금액만 등록 · 단위: 만원</t>
+          <t>※ 인터넷+TV 정책은 매트릭스 기준 통합 1개 (온·오프라인 공통) · 사은품은 3사별 현금 페이백 금액만 등록 · 단위: 만원</t>
         </is>
       </c>
     </row>

--- a/server/public/docs/template-form.xlsx
+++ b/server/public/docs/template-form.xlsx
@@ -19,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0&quot;원&quot;"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Calibri"/>
@@ -172,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -226,6 +228,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -607,6 +612,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="3" t="inlineStr">
@@ -639,6 +645,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="3" t="inlineStr">
@@ -671,6 +678,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="3" t="inlineStr">
@@ -703,6 +711,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="3" t="inlineStr">
@@ -743,6 +752,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="3" t="inlineStr">

--- a/server/public/docs/template-form.xlsx
+++ b/server/public/docs/template-form.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0&quot;원&quot;"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -85,8 +85,46 @@
       <color rgb="0078350f"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00dc2626"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="006366f1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00059669"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0092400e"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002563eb"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00be185d"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="006b7280"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -147,6 +185,31 @@
         <bgColor rgb="00e40981"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00059669"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001f2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00fee2e2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00dbeafe"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00fce7f3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -174,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -233,6 +296,34 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -612,7 +703,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="3" t="inlineStr">
@@ -645,7 +735,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="3" t="inlineStr">
@@ -678,7 +767,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="3" t="inlineStr">
@@ -711,7 +799,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="3" t="inlineStr">
@@ -752,7 +839,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="3" t="inlineStr">
@@ -2352,82 +2438,1510 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>📡 인터넷+TV 사은품 · 통합 1개 (온·오프라인 공통)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>종류</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>SK</t>
-        </is>
-      </c>
-      <c r="C2" s="14" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>📡 인터넷+TV 사은품 · 통합 1개 (온·오프라인 공통) · 63개 상품</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>통신사</t>
+        </is>
+      </c>
+      <c r="C2" s="21" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="D2" s="21" t="inlineStr">
+        <is>
+          <t>상품 구성</t>
+        </is>
+      </c>
+      <c r="E2" s="21" t="inlineStr">
+        <is>
+          <t>사은품(원)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>인터넷 100M</t>
+        </is>
+      </c>
+      <c r="E3" s="25" t="n">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>인터넷 500M</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="n">
+        <v>170000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>인터넷 1G</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="n">
+        <v>170000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 이코노미</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 스탠다드</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 올</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 스탠다드 플러스</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 올 플러스</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 스탠다드 넷플릭스</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 올 넷플릭스</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 스탠다드 넷플릭스 프리미엄</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>인터넷 100M + B tv 올 넷플릭스 프리미엄</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 이코노미</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 스탠다드</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 올</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 스탠다드 플러스</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 올 플러스</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 스탠다드 넷플릭스</t>
+        </is>
+      </c>
+      <c r="E20" s="25" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 올 넷플릭스</t>
+        </is>
+      </c>
+      <c r="E21" s="25" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 스탠다드 넷플릭스 프리미엄</t>
+        </is>
+      </c>
+      <c r="E22" s="25" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>인터넷 500M + B tv 올 넷플릭스 프리미엄</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="n">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 이코노미</t>
+        </is>
+      </c>
+      <c r="E24" s="25" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 스탠다드</t>
+        </is>
+      </c>
+      <c r="E25" s="25" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 올</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 스탠다드 플러스</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 올 플러스</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 스탠다드 넷플릭스</t>
+        </is>
+      </c>
+      <c r="E29" s="25" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 올 넷플릭스</t>
+        </is>
+      </c>
+      <c r="E30" s="25" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 스탠다드 넷플릭스 프리미엄</t>
+        </is>
+      </c>
+      <c r="E31" s="25" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>SKT</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>인터넷 1G + B tv 올 넷플릭스 프리미엄</t>
+        </is>
+      </c>
+      <c r="E32" s="25" t="n">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="27" t="inlineStr">
         <is>
           <t>KT</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>현금</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="n">
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>인터넷 100M</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="n">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>인터넷 500M</t>
+        </is>
+      </c>
+      <c r="E34" s="25" t="n">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>인터넷 1G</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="n">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>인터넷 100M + 지니TV 베이직</t>
+        </is>
+      </c>
+      <c r="E36" s="25" t="n">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>인터넷 100M + 지니TV 라이트</t>
+        </is>
+      </c>
+      <c r="E37" s="25" t="n">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>인터넷 100M + 지니TV 에센스</t>
+        </is>
+      </c>
+      <c r="E38" s="25" t="n">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>인터넷 100M + 지니TV 모든G</t>
+        </is>
+      </c>
+      <c r="E39" s="25" t="n">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>인터넷 100M + 지니TV 디즈니+모든G</t>
+        </is>
+      </c>
+      <c r="E40" s="25" t="n">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>인터넷 500M + 지니TV 베이직</t>
+        </is>
+      </c>
+      <c r="E41" s="25" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>인터넷 500M + 지니TV 라이트</t>
+        </is>
+      </c>
+      <c r="E42" s="25" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>인터넷 500M + 지니TV 에센스</t>
+        </is>
+      </c>
+      <c r="E43" s="25" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>인터넷 500M + 지니TV 모든G</t>
+        </is>
+      </c>
+      <c r="E44" s="25" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>인터넷 500M + 지니TV 디즈니+모든G</t>
+        </is>
+      </c>
+      <c r="E45" s="25" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>인터넷 1G + 지니TV 베이직</t>
+        </is>
+      </c>
+      <c r="E46" s="25" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="22" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>인터넷 1G + 지니TV 라이트</t>
+        </is>
+      </c>
+      <c r="E47" s="25" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C48" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>인터넷 1G + 지니TV 에센스</t>
+        </is>
+      </c>
+      <c r="E48" s="25" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="22" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>인터넷 1G + 지니TV 모든G</t>
+        </is>
+      </c>
+      <c r="E49" s="25" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="27" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C50" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>인터넷 1G + 지니TV 디즈니+모든G</t>
+        </is>
+      </c>
+      <c r="E50" s="25" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>인터넷 100M</t>
+        </is>
+      </c>
+      <c r="E51" s="25" t="n">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="C3" s="17" t="n">
+      <c r="B52" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>인터넷 500M</t>
+        </is>
+      </c>
+      <c r="E52" s="25" t="n">
+        <v>230000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C53" s="24" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>인터넷 1G</t>
+        </is>
+      </c>
+      <c r="E53" s="25" t="n">
+        <v>230000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C54" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>인터넷 100M + U+tv 실속형</t>
+        </is>
+      </c>
+      <c r="E54" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C55" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>인터넷 100M + U+tv 기본형</t>
+        </is>
+      </c>
+      <c r="E55" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C56" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>인터넷 100M + U+tv 프리미엄</t>
+        </is>
+      </c>
+      <c r="E56" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="22" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C57" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>인터넷 100M + U+tv 프리미엄 VOD</t>
+        </is>
+      </c>
+      <c r="E57" s="25" t="n">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="22" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>인터넷 500M + U+tv 실속형</t>
+        </is>
+      </c>
+      <c r="E58" s="25" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="22" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>인터넷 500M + U+tv 기본형</t>
+        </is>
+      </c>
+      <c r="E59" s="25" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="22" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C60" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>인터넷 500M + U+tv 프리미엄</t>
+        </is>
+      </c>
+      <c r="E60" s="25" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="22" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C61" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>인터넷 500M + U+tv 프리미엄 VOD</t>
+        </is>
+      </c>
+      <c r="E61" s="25" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="22" t="n">
         <v>60</v>
       </c>
-      <c r="D3" s="18" t="n">
-        <v>55</v>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>만원 · 샘플</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>※ 인터넷+TV 정책은 매트릭스 기준 통합 1개 (온·오프라인 공통) · 사은품은 3사별 현금 페이백 금액만 등록 · 단위: 만원</t>
+      <c r="B62" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C62" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>인터넷 1G + U+tv 실속형</t>
+        </is>
+      </c>
+      <c r="E62" s="25" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C63" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>인터넷 1G + U+tv 기본형</t>
+        </is>
+      </c>
+      <c r="E63" s="25" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="22" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C64" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>인터넷 1G + U+tv 프리미엄</t>
+        </is>
+      </c>
+      <c r="E64" s="25" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="22" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="28" t="inlineStr">
+        <is>
+          <t>LG U+</t>
+        </is>
+      </c>
+      <c r="C65" s="26" t="inlineStr">
+        <is>
+          <t>결합</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>인터넷 1G + U+tv 프리미엄 VOD</t>
+        </is>
+      </c>
+      <c r="E65" s="25" t="n">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="29" t="inlineStr">
+        <is>
+          <t>※ 인터넷+TV 사은품 정책은 통합 1개 (온·오프라인 공통) · 매장별 차등 없음 · 단위: 원</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A66:E66"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
